--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.20634689762913</v>
+        <v>5.558531370864734</v>
       </c>
       <c r="D2" t="n">
-        <v>25.15820786466964</v>
+        <v>4.088208778008816</v>
       </c>
       <c r="E2" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F2" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.09280712852597</v>
+        <v>8.95258115838547</v>
       </c>
       <c r="D3" t="n">
-        <v>56.35847218410359</v>
+        <v>9.158251729916834</v>
       </c>
       <c r="E3" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F3" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.29029542896333</v>
+        <v>5.897173007206542</v>
       </c>
       <c r="D4" t="n">
-        <v>26.61176771607962</v>
+        <v>4.324412253862939</v>
       </c>
       <c r="E4" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F4" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.82919845922065</v>
+        <v>7.609744749623355</v>
       </c>
       <c r="D5" t="n">
-        <v>30.44627176247391</v>
+        <v>4.947519161402011</v>
       </c>
       <c r="E5" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F5" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.33641193714018</v>
+        <v>6.067166939785279</v>
       </c>
       <c r="D6" t="n">
-        <v>38.42447944660451</v>
+        <v>6.243977910073233</v>
       </c>
       <c r="E6" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F6" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.32005157369731</v>
+        <v>6.552008380725812</v>
       </c>
       <c r="D7" t="n">
-        <v>41.66085116235485</v>
+        <v>6.769888313882663</v>
       </c>
       <c r="E7" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F7" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.47083716915117</v>
+        <v>6.739011039987066</v>
       </c>
       <c r="D8" t="n">
-        <v>29.30017064796722</v>
+        <v>4.761277730294674</v>
       </c>
       <c r="E8" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F8" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.79912800953534</v>
+        <v>5.329858301549494</v>
       </c>
       <c r="D9" t="n">
-        <v>28.66495307146942</v>
+        <v>4.658054874113781</v>
       </c>
       <c r="E9" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F9" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47357578953079</v>
+        <v>4.301956065798755</v>
       </c>
       <c r="D10" t="n">
-        <v>27.78344745811136</v>
+        <v>4.514810211943097</v>
       </c>
       <c r="E10" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F10" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.62607077502951</v>
+        <v>4.164236500942296</v>
       </c>
       <c r="D11" t="n">
-        <v>11.55891984677687</v>
+        <v>1.878324475101241</v>
       </c>
       <c r="E11" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F11" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.92191439000545</v>
+        <v>3.399811088375886</v>
       </c>
       <c r="D12" t="n">
-        <v>17.06446952807226</v>
+        <v>2.772976298311743</v>
       </c>
       <c r="E12" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F12" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.94716541858526</v>
+        <v>3.566414380520106</v>
       </c>
       <c r="D13" t="n">
-        <v>23.28240810172671</v>
+        <v>3.78339131653059</v>
       </c>
       <c r="E13" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F13" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.24949934399311</v>
+        <v>4.91554364339888</v>
       </c>
       <c r="D14" t="n">
-        <v>31.4548169192708</v>
+        <v>5.111407749381505</v>
       </c>
       <c r="E14" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F14" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>29.84821365531088</v>
+        <v>4.850334718988018</v>
       </c>
       <c r="D15" t="n">
-        <v>29.64679797533655</v>
+        <v>4.81760467099219</v>
       </c>
       <c r="E15" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F15" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.65567365318734</v>
+        <v>5.144046968642943</v>
       </c>
       <c r="D16" t="n">
-        <v>31.0496259052013</v>
+        <v>5.045564209595211</v>
       </c>
       <c r="E16" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F16" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8.88546047974307</v>
+        <v>1.443887327958249</v>
       </c>
       <c r="D17" t="n">
-        <v>9.382046179186688</v>
+        <v>1.524582504117837</v>
       </c>
       <c r="E17" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F17" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8.143978864155414</v>
+        <v>1.323396565425255</v>
       </c>
       <c r="D18" t="n">
-        <v>9.115519006156331</v>
+        <v>1.481271838500404</v>
       </c>
       <c r="E18" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F18" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>36.28980205452106</v>
+        <v>5.897092833859673</v>
       </c>
       <c r="D19" t="n">
-        <v>35.31925531963574</v>
+        <v>5.739378989440808</v>
       </c>
       <c r="E19" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F19" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>28.68297818395266</v>
+        <v>4.660983954892306</v>
       </c>
       <c r="D20" t="n">
-        <v>27.99333630292079</v>
+        <v>4.548917149224629</v>
       </c>
       <c r="E20" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F20" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>33.6292449915024</v>
+        <v>5.46475231111914</v>
       </c>
       <c r="D21" t="n">
-        <v>32.38043282842973</v>
+        <v>5.261820334619832</v>
       </c>
       <c r="E21" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F21" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>18.95502685725882</v>
+        <v>3.080191864304559</v>
       </c>
       <c r="D22" t="n">
-        <v>8.074867486950309</v>
+        <v>1.312165966629425</v>
       </c>
       <c r="E22" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F22" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>20.53710947739336</v>
+        <v>3.337280290076422</v>
       </c>
       <c r="D23" t="n">
-        <v>19.2700094417346</v>
+        <v>3.131376534281873</v>
       </c>
       <c r="E23" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F23" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>23.40176107421742</v>
+        <v>3.80278617456033</v>
       </c>
       <c r="D24" t="n">
-        <v>23.24091366498761</v>
+        <v>3.776648470560487</v>
       </c>
       <c r="E24" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F24" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>23.3753614154434</v>
+        <v>3.798496230009553</v>
       </c>
       <c r="D25" t="n">
-        <v>20.75761447832914</v>
+        <v>3.373112352728486</v>
       </c>
       <c r="E25" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F25" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>14.52075054188727</v>
+        <v>2.359621963056681</v>
       </c>
       <c r="D26" t="n">
-        <v>13.91890695032259</v>
+        <v>2.261822379427421</v>
       </c>
       <c r="E26" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F26" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>42.12920901243738</v>
+        <v>6.845996464521074</v>
       </c>
       <c r="D27" t="n">
-        <v>37.41419543647451</v>
+        <v>6.079806758427109</v>
       </c>
       <c r="E27" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F27" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>27.80083069120856</v>
+        <v>4.517634987321391</v>
       </c>
       <c r="D28" t="n">
-        <v>26.39381982031368</v>
+        <v>4.288995720800973</v>
       </c>
       <c r="E28" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F28" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>37.2776249176594</v>
+        <v>6.057614049119653</v>
       </c>
       <c r="D29" t="n">
-        <v>35.98559407927129</v>
+        <v>5.847659037881585</v>
       </c>
       <c r="E29" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F29" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>48.75657268608886</v>
+        <v>7.92294306148944</v>
       </c>
       <c r="D30" t="n">
-        <v>47.43475454589966</v>
+        <v>7.708147613708696</v>
       </c>
       <c r="E30" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F30" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>38.2048110770982</v>
+        <v>6.208281800028457</v>
       </c>
       <c r="D31" t="n">
-        <v>37.84146719724782</v>
+        <v>6.149238419552771</v>
       </c>
       <c r="E31" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F31" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>39.02587564814031</v>
+        <v>6.3417047928228</v>
       </c>
       <c r="D32" t="n">
-        <v>38.13992198691518</v>
+        <v>6.197737322873717</v>
       </c>
       <c r="E32" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F32" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>42.48105358720768</v>
+        <v>6.903171207921249</v>
       </c>
       <c r="D33" t="n">
-        <v>41.83947249969468</v>
+        <v>6.798914281200386</v>
       </c>
       <c r="E33" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F33" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>66.59140490389514</v>
+        <v>10.82110329688296</v>
       </c>
       <c r="D34" t="n">
-        <v>65.26974906366388</v>
+        <v>10.60633422284538</v>
       </c>
       <c r="E34" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F34" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>67.52456860018191</v>
+        <v>10.97274239752956</v>
       </c>
       <c r="D35" t="n">
-        <v>66.2352794148881</v>
+        <v>10.76323290491932</v>
       </c>
       <c r="E35" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F35" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>63.76427095386197</v>
+        <v>10.36169403000257</v>
       </c>
       <c r="D36" t="n">
-        <v>62.84842991544524</v>
+        <v>10.21286986125985</v>
       </c>
       <c r="E36" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F36" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>75.03517674462691</v>
+        <v>12.19321622100187</v>
       </c>
       <c r="D37" t="n">
-        <v>73.878665482222</v>
+        <v>12.00528314086108</v>
       </c>
       <c r="E37" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F37" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>90.33952024110637</v>
+        <v>14.68017203917979</v>
       </c>
       <c r="D38" t="n">
-        <v>89.12827116640686</v>
+        <v>14.48334406454112</v>
       </c>
       <c r="E38" t="n">
-        <v>17.71270827966753</v>
+        <v>2.878315095445974</v>
       </c>
       <c r="F38" t="n">
-        <v>18.32375176992349</v>
+        <v>2.977609662612568</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
